--- a/docs/StructureDefinition-OperatingRoom1317.xlsx
+++ b/docs/StructureDefinition-OperatingRoom1317.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-OperatingRoom1317.xlsx
+++ b/docs/StructureDefinition-OperatingRoom1317.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -260,14 +260,14 @@
     <t>NAME (-.01)</t>
   </si>
   <si>
-    <t>OperatingRoom1317.telehone</t>
+    <t>OperatingRoom1317.telephone</t>
   </si>
   <si>
     <t xml:space="preserve">Element
 </t>
   </si>
   <si>
-    <t>TELEHONE (-3)</t>
+    <t>TELEPHONE (-3)</t>
   </si>
   <si>
     <t>OperatingRoom1317.inactive</t>
@@ -588,8 +588,8 @@
   <dimension ref="A1:AJ5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="28.8203125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="28.8203125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="29.984375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="29.984375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="8.95703125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
@@ -619,7 +619,7 @@
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="28.8203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>

--- a/docs/StructureDefinition-OperatingRoom1317.xlsx
+++ b/docs/StructureDefinition-OperatingRoom1317.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-OperatingRoom1317.xlsx
+++ b/docs/StructureDefinition-OperatingRoom1317.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-OperatingRoom1317.xlsx
+++ b/docs/StructureDefinition-OperatingRoom1317.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -283,7 +283,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFOperatingRoomStatus-vista</t>
+    <t>http://va.gov/fhir/ValueSet/OperatingRoomStatus-vista</t>
   </si>
 </sst>
 </file>
@@ -613,7 +613,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="56.0234375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="51.296875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-OperatingRoom1317.xlsx
+++ b/docs/StructureDefinition-OperatingRoom1317.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-OperatingRoom1317.xlsx
+++ b/docs/StructureDefinition-OperatingRoom1317.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-OperatingRoom1317.xlsx
+++ b/docs/StructureDefinition-OperatingRoom1317.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-OperatingRoom1317.xlsx
+++ b/docs/StructureDefinition-OperatingRoom1317.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-OperatingRoom1317.xlsx
+++ b/docs/StructureDefinition-OperatingRoom1317.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-OperatingRoom1317.xlsx
+++ b/docs/StructureDefinition-OperatingRoom1317.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-OperatingRoom1317.xlsx
+++ b/docs/StructureDefinition-OperatingRoom1317.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-OperatingRoom1317.xlsx
+++ b/docs/StructureDefinition-OperatingRoom1317.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-OperatingRoom1317.xlsx
+++ b/docs/StructureDefinition-OperatingRoom1317.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-OperatingRoom1317.xlsx
+++ b/docs/StructureDefinition-OperatingRoom1317.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-OperatingRoom1317.xlsx
+++ b/docs/StructureDefinition-OperatingRoom1317.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-OperatingRoom1317.xlsx
+++ b/docs/StructureDefinition-OperatingRoom1317.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-OperatingRoom1317.xlsx
+++ b/docs/StructureDefinition-OperatingRoom1317.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-OperatingRoom1317.xlsx
+++ b/docs/StructureDefinition-OperatingRoom1317.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-OperatingRoom1317.xlsx
+++ b/docs/StructureDefinition-OperatingRoom1317.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
